--- a/frontend/public/Excels Templates/SaleTemplates.xlsx
+++ b/frontend/public/Excels Templates/SaleTemplates.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{359F2273-BEE9-489E-8058-48111B834242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sales Report" state="visible" r:id="rId4"/>
+    <sheet name="20 Package" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -22,6 +26,12 @@
     <t>Bar Code</t>
   </si>
   <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Sent to Yukesh 60 RMB</t>
+  </si>
+  <si>
     <t>Location</t>
   </si>
   <si>
@@ -31,13 +41,7 @@
     <t>Price Type</t>
   </si>
   <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Date</t>
+    <t>Sold Price</t>
   </si>
   <si>
     <t>Sold By</t>
@@ -46,20 +50,28 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri(BODY)"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="0"/>
-      <sz val="13"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -71,11 +83,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF720E20"/>
+        <fgColor rgb="FF711515"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -83,20 +96,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -105,6 +117,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF711515"/>
+      <color rgb="FF9F1D1D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -121,19 +139,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>320000</xdr:colOff>
+      <xdr:colOff>300637</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>96000</xdr:rowOff>
+      <xdr:rowOff>96018</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>320000</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>47188</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>297000</xdr:rowOff>
+      <xdr:rowOff>296754</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -152,8 +170,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="7024166" y="96018"/>
+          <a:ext cx="1443442" cy="584937"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -176,44 +194,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -241,14 +259,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -276,6 +311,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -287,280 +339,226 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I71"/>
+  <sheetFormatPr defaultColWidth="15.3046875" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="21.921875" customWidth="1"/>
+    <col min="7" max="7" width="23.53515625" customWidth="1"/>
+    <col min="9" max="9" width="24.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
-      <c r="J1"/>
+    <row r="1" spans="1:9" ht="30" customHeight="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2"/>
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
+    <row r="2" spans="1:9" ht="30" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
-    <row r="3" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:9" ht="30" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="30" customHeight="1">
+      <c r="A61" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="71" spans="1:2" ht="30" customHeight="1">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A1:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>